--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_all_temperatures.xlsx
@@ -485,15 +485,9 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.3</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -508,15 +502,9 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>25.4</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -531,15 +519,9 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="E4" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F4" t="n">
-        <v>26.5</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -554,15 +536,9 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>27</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -577,15 +553,9 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -600,15 +570,9 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>30</v>
-      </c>
-      <c r="E7" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -623,15 +587,9 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E8" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>27.2</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -646,15 +604,9 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>26.6</v>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -669,15 +621,9 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="F10" t="n">
-        <v>26.3</v>
-      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -692,15 +638,9 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -715,15 +655,9 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -738,15 +672,9 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F13" t="n">
-        <v>26.3</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -761,15 +689,9 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>26.5</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -784,15 +706,9 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E15" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F15" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -807,15 +723,9 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>27</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -830,15 +740,9 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -853,15 +757,9 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>21</v>
-      </c>
-      <c r="F18" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -876,15 +774,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E19" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -899,15 +791,9 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F20" t="n">
-        <v>26.1</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -922,15 +808,9 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>26</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -945,15 +825,9 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F22" t="n">
-        <v>25.2</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -968,15 +842,9 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E23" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F23" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -991,15 +859,9 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F24" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1014,15 +876,9 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="n">
-        <v>31</v>
-      </c>
-      <c r="E25" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F25" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1037,15 +893,9 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F26" t="n">
-        <v>26.5</v>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -1060,15 +910,9 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E27" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>26.1</v>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1083,15 +927,9 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E28" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F28" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1106,15 +944,9 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E29" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>25.6</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1129,15 +961,9 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="E30" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1152,15 +978,9 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="n">
-        <v>30</v>
-      </c>
-      <c r="E31" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F31" t="n">
-        <v>25.6</v>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -1175,15 +995,9 @@
       <c r="C32" t="n">
         <v>31</v>
       </c>
-      <c r="D32" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E32" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F32" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1222,13 +1036,13 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="E34" t="n">
-        <v>20.8</v>
+        <v>19</v>
       </c>
       <c r="F34" t="n">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1245,13 +1059,13 @@
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="E35" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="F35" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1293,12 +1107,8 @@
       <c r="D37" t="n">
         <v>33.3</v>
       </c>
-      <c r="E37" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F37" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1314,13 +1124,13 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>33.13</v>
+        <v>32.8</v>
       </c>
       <c r="E38" t="n">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
       <c r="F38" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -1337,13 +1147,13 @@
         <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>32.8</v>
+        <v>29</v>
       </c>
       <c r="E39" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="F39" t="n">
-        <v>26.5</v>
+        <v>24.9</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -1359,15 +1169,9 @@
       <c r="C40" t="n">
         <v>8</v>
       </c>
-      <c r="D40" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E40" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F40" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1382,15 +1186,9 @@
       <c r="C41" t="n">
         <v>9</v>
       </c>
-      <c r="D41" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E41" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F41" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1405,15 +1203,9 @@
       <c r="C42" t="n">
         <v>10</v>
       </c>
-      <c r="D42" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E42" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F42" t="n">
-        <v>25.3</v>
-      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1428,15 +1220,9 @@
       <c r="C43" t="n">
         <v>11</v>
       </c>
-      <c r="D43" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E43" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>25.7</v>
-      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1452,13 +1238,13 @@
         <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>32.1</v>
+        <v>29.7</v>
       </c>
       <c r="E44" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
       <c r="F44" t="n">
-        <v>26.4</v>
+        <v>24.7</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -1475,13 +1261,13 @@
         <v>13</v>
       </c>
       <c r="D45" t="n">
-        <v>29.7</v>
+        <v>30.9</v>
       </c>
       <c r="E45" t="n">
-        <v>19.7</v>
+        <v>18.1</v>
       </c>
       <c r="F45" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1498,13 +1284,13 @@
         <v>14</v>
       </c>
       <c r="D46" t="n">
-        <v>30.2</v>
+        <v>31.4</v>
       </c>
       <c r="E46" t="n">
-        <v>18.1</v>
+        <v>26.8</v>
       </c>
       <c r="F46" t="n">
-        <v>24.1</v>
+        <v>29</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -1520,15 +1306,9 @@
       <c r="C47" t="n">
         <v>15</v>
       </c>
-      <c r="D47" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E47" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1544,10 +1324,14 @@
         <v>16</v>
       </c>
       <c r="D48" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+        <v>31.7</v>
+      </c>
+      <c r="E48" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>26.1</v>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1562,15 +1346,9 @@
       <c r="C49" t="n">
         <v>17</v>
       </c>
-      <c r="D49" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E49" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F49" t="n">
-        <v>26.1</v>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1585,9 +1363,7 @@
       <c r="C50" t="n">
         <v>18</v>
       </c>
-      <c r="D50" t="n">
-        <v>32.9</v>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
@@ -1604,15 +1380,9 @@
       <c r="C51" t="n">
         <v>19</v>
       </c>
-      <c r="D51" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E51" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F51" t="n">
-        <v>26.2</v>
-      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -1627,15 +1397,9 @@
       <c r="C52" t="n">
         <v>20</v>
       </c>
-      <c r="D52" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E52" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F52" t="n">
-        <v>24.8</v>
-      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1650,15 +1414,9 @@
       <c r="C53" t="n">
         <v>21</v>
       </c>
-      <c r="D53" t="n">
-        <v>29</v>
-      </c>
-      <c r="E53" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F53" t="n">
-        <v>24.7</v>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1674,13 +1432,13 @@
         <v>22</v>
       </c>
       <c r="D54" t="n">
-        <v>25.2</v>
+        <v>30.6</v>
       </c>
       <c r="E54" t="n">
-        <v>20.6</v>
+        <v>19.2</v>
       </c>
       <c r="F54" t="n">
-        <v>22.9</v>
+        <v>24.9</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -1696,15 +1454,9 @@
       <c r="C55" t="n">
         <v>23</v>
       </c>
-      <c r="D55" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E55" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -1719,15 +1471,9 @@
       <c r="C56" t="n">
         <v>24</v>
       </c>
-      <c r="D56" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E56" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F56" t="n">
-        <v>24.1</v>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1742,15 +1488,9 @@
       <c r="C57" t="n">
         <v>25</v>
       </c>
-      <c r="D57" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E57" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1765,12 +1505,8 @@
       <c r="C58" t="n">
         <v>26</v>
       </c>
-      <c r="D58" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E58" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
         <v>25</v>
       </c>
@@ -1788,14 +1524,10 @@
       <c r="C59" t="n">
         <v>27</v>
       </c>
-      <c r="D59" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E59" t="n">
-        <v>20.8</v>
-      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
@@ -1811,14 +1543,10 @@
       <c r="C60" t="n">
         <v>28</v>
       </c>
-      <c r="D60" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E60" t="n">
-        <v>20.3</v>
-      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
@@ -1835,13 +1563,13 @@
         <v>29</v>
       </c>
       <c r="D61" t="n">
-        <v>30.8</v>
+        <v>36.9</v>
       </c>
       <c r="E61" t="n">
-        <v>21.1</v>
+        <v>14.3</v>
       </c>
       <c r="F61" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
@@ -1861,10 +1589,10 @@
         <v>30.8</v>
       </c>
       <c r="E62" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="F62" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_all_temperatures.xlsx
@@ -485,9 +485,15 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -502,9 +508,15 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>25.4</v>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -519,9 +531,15 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>26.5</v>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -536,9 +554,15 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27.3</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -553,9 +577,15 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.6</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -570,9 +600,15 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -587,9 +623,15 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27.2</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -604,9 +646,15 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>26.6</v>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -621,9 +669,15 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>26.3</v>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -638,9 +692,15 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>26.7</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -655,9 +715,15 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>26.7</v>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -672,9 +738,15 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26.5</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -689,9 +761,15 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>26.4</v>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -706,9 +784,15 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>25.9</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -723,9 +807,15 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>27</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -740,9 +830,15 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>23.5</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -757,9 +853,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" t="n">
+        <v>29.1</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -774,9 +876,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -792,7 +900,9 @@
         <v>19</v>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>20.5</v>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -808,9 +918,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>26</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -825,9 +941,15 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>25.2</v>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -842,9 +964,15 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F23" t="n">
+        <v>24.4</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -859,9 +987,15 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>26.7</v>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -876,9 +1010,15 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>25.9</v>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -893,9 +1033,15 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F26" t="n">
+        <v>26.5</v>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -910,9 +1056,15 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>32</v>
+      </c>
+      <c r="E27" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>26.1</v>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -927,9 +1079,15 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E28" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>25.9</v>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -944,9 +1102,15 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>25.6</v>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -961,9 +1125,15 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>25.9</v>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -978,9 +1148,15 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>25.6</v>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -995,9 +1171,15 @@
       <c r="C32" t="n">
         <v>31</v>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>26.9</v>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1036,13 +1218,13 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>31.4</v>
+        <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>19</v>
+        <v>20.8</v>
       </c>
       <c r="F34" t="n">
-        <v>25.2</v>
+        <v>25.9</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1059,13 +1241,13 @@
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="E35" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="F35" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1082,10 +1264,10 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>32.4</v>
+        <v>32.6</v>
       </c>
       <c r="E36" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="F36" t="n">
         <v>26.7</v>
@@ -1105,10 +1287,14 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+        <v>33.2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F37" t="n">
+        <v>27.5</v>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
@@ -1124,13 +1310,13 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>32.8</v>
+        <v>33.4</v>
       </c>
       <c r="E38" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="F38" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
@@ -1147,13 +1333,13 @@
         <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>32.8</v>
       </c>
       <c r="E39" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="F39" t="n">
-        <v>24.9</v>
+        <v>26.5</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
@@ -1169,9 +1355,15 @@
       <c r="C40" t="n">
         <v>8</v>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>29</v>
+      </c>
+      <c r="E40" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -1186,9 +1378,15 @@
       <c r="C41" t="n">
         <v>9</v>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E41" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>23.6</v>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
@@ -1203,9 +1401,15 @@
       <c r="C42" t="n">
         <v>10</v>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F42" t="n">
+        <v>25.4</v>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1220,9 +1424,15 @@
       <c r="C43" t="n">
         <v>11</v>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>25.7</v>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -1238,13 +1448,13 @@
         <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>29.7</v>
+        <v>32.1</v>
       </c>
       <c r="E44" t="n">
-        <v>19.7</v>
+        <v>20.5</v>
       </c>
       <c r="F44" t="n">
-        <v>24.7</v>
+        <v>26.3</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
@@ -1260,15 +1470,9 @@
       <c r="C45" t="n">
         <v>13</v>
       </c>
-      <c r="D45" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E45" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1284,13 +1488,13 @@
         <v>14</v>
       </c>
       <c r="D46" t="n">
-        <v>31.4</v>
+        <v>30.1</v>
       </c>
       <c r="E46" t="n">
-        <v>26.8</v>
+        <v>18.1</v>
       </c>
       <c r="F46" t="n">
-        <v>29</v>
+        <v>24.1</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
@@ -1323,15 +1527,9 @@
       <c r="C48" t="n">
         <v>16</v>
       </c>
-      <c r="D48" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E48" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F48" t="n">
-        <v>26.1</v>
-      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1346,9 +1544,15 @@
       <c r="C49" t="n">
         <v>17</v>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E49" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>26.1</v>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -1380,9 +1584,15 @@
       <c r="C51" t="n">
         <v>19</v>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E51" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F51" t="n">
+        <v>26.2</v>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
@@ -1397,9 +1607,15 @@
       <c r="C52" t="n">
         <v>20</v>
       </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F52" t="n">
+        <v>24.8</v>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
@@ -1414,9 +1630,15 @@
       <c r="C53" t="n">
         <v>21</v>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>29</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F53" t="n">
+        <v>24.7</v>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
@@ -1432,13 +1654,13 @@
         <v>22</v>
       </c>
       <c r="D54" t="n">
-        <v>30.6</v>
+        <v>25.2</v>
       </c>
       <c r="E54" t="n">
-        <v>19.2</v>
+        <v>20.6</v>
       </c>
       <c r="F54" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -1454,9 +1676,15 @@
       <c r="C55" t="n">
         <v>23</v>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E55" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F55" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -1471,9 +1699,15 @@
       <c r="C56" t="n">
         <v>24</v>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E56" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F56" t="n">
+        <v>24.1</v>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
@@ -1488,9 +1722,15 @@
       <c r="C57" t="n">
         <v>25</v>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E57" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F57" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -1507,9 +1747,7 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="n">
-        <v>25</v>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -1524,8 +1762,12 @@
       <c r="C59" t="n">
         <v>27</v>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E59" t="n">
+        <v>20.6</v>
+      </c>
       <c r="F59" t="n">
         <v>25.7</v>
       </c>
@@ -1543,8 +1785,12 @@
       <c r="C60" t="n">
         <v>28</v>
       </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>20.8</v>
+      </c>
       <c r="F60" t="n">
         <v>25.2</v>
       </c>
@@ -1563,10 +1809,10 @@
         <v>29</v>
       </c>
       <c r="D61" t="n">
-        <v>36.9</v>
+        <v>30.8</v>
       </c>
       <c r="E61" t="n">
-        <v>14.3</v>
+        <v>20.3</v>
       </c>
       <c r="F61" t="n">
         <v>25.6</v>
@@ -1589,10 +1835,10 @@
         <v>30.8</v>
       </c>
       <c r="E62" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="F62" t="n">
-        <v>25.6</v>
+        <v>25.9</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_all_temperatures.xlsx
@@ -489,7 +489,7 @@
         <v>28.1</v>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="F2" t="n">
         <v>24.1</v>
@@ -558,10 +558,10 @@
         <v>34.7</v>
       </c>
       <c r="E5" t="n">
-        <v>19.9</v>
+        <v>7.3</v>
       </c>
       <c r="F5" t="n">
-        <v>27.3</v>
+        <v>21</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -601,10 +601,10 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="F7" t="n">
         <v>24.9</v>
@@ -624,13 +624,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>31.8</v>
+        <v>32.4</v>
       </c>
       <c r="E8" t="n">
         <v>22.6</v>
       </c>
       <c r="F8" t="n">
-        <v>27.2</v>
+        <v>27.6</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -647,10 +647,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>33.1</v>
+        <v>32.8</v>
       </c>
       <c r="E9" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="F9" t="n">
         <v>26.6</v>
@@ -693,13 +693,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="E11" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="F11" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -716,13 +716,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="F12" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -742,10 +742,10 @@
         <v>30.4</v>
       </c>
       <c r="E13" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="F13" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -762,10 +762,10 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="E14" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="F14" t="n">
         <v>26.4</v>
@@ -831,10 +831,10 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="E17" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="F17" t="n">
         <v>23.5</v>
@@ -853,15 +853,9 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>21</v>
-      </c>
-      <c r="F18" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -876,15 +870,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -899,11 +887,15 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>31.7</v>
+      </c>
       <c r="E20" t="n">
         <v>20.5</v>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>26.1</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -918,15 +910,9 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>26</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -991,7 +977,7 @@
         <v>31.9</v>
       </c>
       <c r="E24" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="F24" t="n">
         <v>26.7</v>
@@ -1057,10 +1043,10 @@
         <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>32.2</v>
       </c>
       <c r="E27" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="F27" t="n">
         <v>26.1</v>
@@ -1080,10 +1066,10 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="F28" t="n">
         <v>25.9</v>
@@ -1126,7 +1112,7 @@
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="E30" t="n">
         <v>20.2</v>
@@ -1149,10 +1135,10 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>30.1</v>
+        <v>29.9</v>
       </c>
       <c r="E31" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="F31" t="n">
         <v>25.6</v>
@@ -1221,7 +1207,7 @@
         <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F34" t="n">
         <v>25.9</v>
@@ -1241,13 +1227,13 @@
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="E35" t="n">
         <v>21.1</v>
       </c>
       <c r="F35" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1264,13 +1250,13 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>32.6</v>
+        <v>36.4</v>
       </c>
       <c r="E36" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="F36" t="n">
-        <v>26.7</v>
+        <v>28.7</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -1290,10 +1276,10 @@
         <v>33.2</v>
       </c>
       <c r="E37" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="F37" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -1310,7 +1296,7 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="E38" t="n">
         <v>19.9</v>
@@ -1356,7 +1342,7 @@
         <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="E40" t="n">
         <v>20.8</v>
@@ -1379,13 +1365,13 @@
         <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="E41" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="F41" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1402,13 +1388,13 @@
         <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
       <c r="E42" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="F42" t="n">
-        <v>25.4</v>
+        <v>25.9</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1448,7 +1434,7 @@
         <v>12</v>
       </c>
       <c r="D44" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="E44" t="n">
         <v>20.5</v>
@@ -1470,9 +1456,15 @@
       <c r="C45" t="n">
         <v>13</v>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E45" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F45" t="n">
+        <v>24.7</v>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -1491,7 +1483,7 @@
         <v>30.1</v>
       </c>
       <c r="E46" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="F46" t="n">
         <v>24.1</v>
@@ -1510,9 +1502,15 @@
       <c r="C47" t="n">
         <v>15</v>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>32</v>
+      </c>
+      <c r="E47" t="n">
+        <v>18</v>
+      </c>
+      <c r="F47" t="n">
+        <v>25</v>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
@@ -1527,9 +1525,15 @@
       <c r="C48" t="n">
         <v>16</v>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>30</v>
+      </c>
+      <c r="E48" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F48" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
@@ -1567,9 +1571,15 @@
       <c r="C50" t="n">
         <v>18</v>
       </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>37</v>
+      </c>
+      <c r="E50" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>28.1</v>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
@@ -1608,10 +1618,10 @@
         <v>20</v>
       </c>
       <c r="D52" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="E52" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F52" t="n">
         <v>24.8</v>
@@ -1677,10 +1687,10 @@
         <v>23</v>
       </c>
       <c r="D55" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="E55" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="F55" t="n">
         <v>24.9</v>
@@ -1700,7 +1710,7 @@
         <v>24</v>
       </c>
       <c r="D56" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="E56" t="n">
         <v>18.8</v>
@@ -1723,10 +1733,10 @@
         <v>25</v>
       </c>
       <c r="D57" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="E57" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="F57" t="n">
         <v>24.9</v>
@@ -1745,9 +1755,15 @@
       <c r="C58" t="n">
         <v>26</v>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>25</v>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -1809,10 +1825,10 @@
         <v>29</v>
       </c>
       <c r="D61" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="E61" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="F61" t="n">
         <v>25.6</v>
@@ -1832,10 +1848,10 @@
         <v>30</v>
       </c>
       <c r="D62" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="E62" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="F62" t="n">
         <v>25.9</v>

--- a/results/04_final_refined_daily_hydroclimate_data/203/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Daily_all_temperatures.xlsx
@@ -486,10 +486,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
       <c r="E2" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="F2" t="n">
         <v>24.1</v>
@@ -555,13 +555,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="E5" t="n">
-        <v>7.3</v>
+        <v>19.3</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -624,13 +624,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>32.4</v>
+        <v>31.8</v>
       </c>
       <c r="E8" t="n">
         <v>22.6</v>
       </c>
       <c r="F8" t="n">
-        <v>27.6</v>
+        <v>27.2</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -716,7 +716,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="E12" t="n">
         <v>21.2</v>
@@ -762,13 +762,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>31.4</v>
+        <v>38.5</v>
       </c>
       <c r="E14" t="n">
-        <v>21.5</v>
+        <v>18.5</v>
       </c>
       <c r="F14" t="n">
-        <v>26.4</v>
+        <v>28.5</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -788,7 +788,7 @@
         <v>30.6</v>
       </c>
       <c r="E15" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="F15" t="n">
         <v>25.9</v>
@@ -853,9 +853,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" t="n">
+        <v>23.1</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -870,9 +876,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>25.5</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -888,7 +900,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="E20" t="n">
         <v>20.5</v>
@@ -910,9 +922,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>26</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -931,10 +949,10 @@
         <v>31.1</v>
       </c>
       <c r="E22" t="n">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="F22" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -977,10 +995,10 @@
         <v>31.9</v>
       </c>
       <c r="E24" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="F24" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1000,7 +1018,7 @@
         <v>31.1</v>
       </c>
       <c r="E25" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F25" t="n">
         <v>25.9</v>
@@ -1043,10 +1061,10 @@
         <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>32.2</v>
+        <v>31.9</v>
       </c>
       <c r="E27" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="F27" t="n">
         <v>26.1</v>
@@ -1115,7 +1133,7 @@
         <v>31.6</v>
       </c>
       <c r="E30" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="F30" t="n">
         <v>25.9</v>
@@ -1135,13 +1153,13 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>29.9</v>
+        <v>28.1</v>
       </c>
       <c r="E31" t="n">
         <v>21.3</v>
       </c>
       <c r="F31" t="n">
-        <v>25.6</v>
+        <v>24.7</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1181,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="E33" t="n">
         <v>22.7</v>
@@ -1204,10 +1222,10 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="E34" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F34" t="n">
         <v>25.9</v>
@@ -1227,13 +1245,13 @@
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E35" t="n">
         <v>21.1</v>
       </c>
       <c r="F35" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1250,13 +1268,13 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>36.4</v>
+        <v>32.4</v>
       </c>
       <c r="E36" t="n">
         <v>21</v>
       </c>
       <c r="F36" t="n">
-        <v>28.7</v>
+        <v>26.7</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
@@ -1273,13 +1291,13 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>33.2</v>
+        <v>33.3</v>
       </c>
       <c r="E37" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="F37" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
@@ -1342,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="E40" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F40" t="n">
         <v>24.9</v>
@@ -1365,13 +1383,13 @@
         <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="E41" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="F41" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1388,13 +1406,13 @@
         <v>10</v>
       </c>
       <c r="D42" t="n">
-        <v>32.3</v>
+        <v>31.3</v>
       </c>
       <c r="E42" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="F42" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1411,7 +1429,7 @@
         <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="E43" t="n">
         <v>19.2</v>
@@ -1483,7 +1501,7 @@
         <v>30.1</v>
       </c>
       <c r="E46" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="F46" t="n">
         <v>24.1</v>
@@ -1503,10 +1521,10 @@
         <v>15</v>
       </c>
       <c r="D47" t="n">
-        <v>32</v>
+        <v>31.2</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="F47" t="n">
         <v>25</v>
@@ -1595,13 +1613,13 @@
         <v>19</v>
       </c>
       <c r="D51" t="n">
-        <v>32.6</v>
+        <v>33.8</v>
       </c>
       <c r="E51" t="n">
         <v>19.8</v>
       </c>
       <c r="F51" t="n">
-        <v>26.2</v>
+        <v>26.8</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
@@ -1618,10 +1636,10 @@
         <v>20</v>
       </c>
       <c r="D52" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="E52" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F52" t="n">
         <v>24.8</v>
